--- a/Ejemplo_Calculo_Costos.xlsx
+++ b/Ejemplo_Calculo_Costos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aad5c92cd729ce53/Desktop/Canelon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="684" documentId="8_{73BCACF4-02CA-48FB-B2BD-168834A595B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F9C72A3-5759-41B5-AD67-3DCE7535C1DE}"/>
+  <xr:revisionPtr revIDLastSave="686" documentId="8_{73BCACF4-02CA-48FB-B2BD-168834A595B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D710F3A-CE42-478E-B6BC-24E254D0972B}"/>
   <bookViews>
-    <workbookView xWindow="3408" yWindow="72" windowWidth="19680" windowHeight="11952" xr2:uid="{3A4320B7-4EBE-4B4B-8C38-391152CD5001}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3A4320B7-4EBE-4B4B-8C38-391152CD5001}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -427,7 +427,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -543,99 +543,93 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -660,6 +654,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1035,15 +1033,15 @@
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="2:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
       <c r="I6" s="5"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -1052,10 +1050,10 @@
       <c r="N6" s="3"/>
     </row>
     <row r="7" spans="2:17" s="4" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="67"/>
+      <c r="C7" s="50"/>
       <c r="D7" s="35" t="s">
         <v>1</v>
       </c>
@@ -1079,10 +1077,10 @@
       <c r="N7" s="3"/>
     </row>
     <row r="8" spans="2:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="58"/>
+      <c r="C8" s="46"/>
       <c r="D8" s="36" t="s">
         <v>4</v>
       </c>
@@ -1109,10 +1107,10 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="2:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="58"/>
+      <c r="C9" s="46"/>
       <c r="D9" s="36" t="s">
         <v>4</v>
       </c>
@@ -1139,10 +1137,10 @@
       <c r="N9" s="3"/>
     </row>
     <row r="10" spans="2:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="58"/>
+      <c r="C10" s="46"/>
       <c r="D10" s="36" t="s">
         <v>6</v>
       </c>
@@ -1169,10 +1167,10 @@
       <c r="N10" s="3"/>
     </row>
     <row r="11" spans="2:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="58"/>
+      <c r="C11" s="46"/>
       <c r="D11" s="20" t="s">
         <v>4</v>
       </c>
@@ -1199,14 +1197,14 @@
       <c r="N11" s="3"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="65"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="71">
+      <c r="E12" s="42">
         <f>F12/7.63</f>
         <v>51.114023591087815</v>
       </c>
@@ -1227,10 +1225,10 @@
       <c r="Q12"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="60" t="s">
+      <c r="B13" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="61"/>
+      <c r="C13" s="52"/>
       <c r="D13" s="37" t="s">
         <v>13</v>
       </c>
@@ -1254,8 +1252,8 @@
       <c r="Q13"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="57"/>
-      <c r="C14" s="58"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="46"/>
       <c r="D14" s="10"/>
       <c r="E14" s="12"/>
       <c r="F14" s="14">
@@ -1272,8 +1270,8 @@
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="57"/>
-      <c r="C15" s="58"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="46"/>
       <c r="D15" s="10"/>
       <c r="E15" s="12"/>
       <c r="F15" s="14">
@@ -1290,8 +1288,8 @@
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="57"/>
-      <c r="C16" s="58"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="46"/>
       <c r="D16" s="10"/>
       <c r="E16" s="12"/>
       <c r="F16" s="14">
@@ -1308,10 +1306,10 @@
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="62"/>
+      <c r="C17" s="54"/>
       <c r="D17" s="25"/>
       <c r="E17" s="11">
         <f>SUM(E8:E11)</f>
@@ -1340,39 +1338,39 @@
       <c r="H18" s="18"/>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="H20" s="48" t="s">
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
+      <c r="H20" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="50"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="68"/>
       <c r="R20" s="1"/>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="59"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="72" t="s">
+      <c r="E21" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="72" t="s">
+      <c r="F21" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="51" t="s">
+      <c r="H21" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="52"/>
+      <c r="I21" s="70"/>
       <c r="J21" s="29" t="s">
         <v>28</v>
       </c>
@@ -1383,10 +1381,10 @@
       <c r="S21" s="1"/>
     </row>
     <row r="22" spans="2:19" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="42"/>
+      <c r="C22" s="62"/>
       <c r="D22" s="9">
         <v>7</v>
       </c>
@@ -1398,10 +1396,10 @@
         <f>E22/7.63</f>
         <v>220.18348623853211</v>
       </c>
-      <c r="H22" s="43" t="s">
+      <c r="H22" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="I22" s="44"/>
+      <c r="I22" s="58"/>
       <c r="J22" s="30">
         <v>1</v>
       </c>
@@ -1413,10 +1411,10 @@
       <c r="S22" s="1"/>
     </row>
     <row r="23" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="42"/>
+      <c r="C23" s="62"/>
       <c r="D23" s="9">
         <v>2</v>
       </c>
@@ -1428,10 +1426,10 @@
         <f t="shared" ref="F23:F41" si="8">E23/7.63</f>
         <v>62.909567496723461</v>
       </c>
-      <c r="H23" s="43" t="s">
+      <c r="H23" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="I23" s="44"/>
+      <c r="I23" s="58"/>
       <c r="J23" s="30">
         <v>1</v>
       </c>
@@ -1442,10 +1440,10 @@
       <c r="Q23"/>
     </row>
     <row r="24" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="42"/>
+      <c r="C24" s="62"/>
       <c r="D24" s="9">
         <v>5</v>
       </c>
@@ -1457,10 +1455,10 @@
         <f t="shared" si="8"/>
         <v>157.27391874180864</v>
       </c>
-      <c r="H24" s="43" t="s">
+      <c r="H24" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="I24" s="44"/>
+      <c r="I24" s="58"/>
       <c r="J24" s="30">
         <v>2</v>
       </c>
@@ -1471,10 +1469,10 @@
       <c r="Q24"/>
     </row>
     <row r="25" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="56"/>
+      <c r="C25" s="64"/>
       <c r="D25" s="9">
         <v>5</v>
       </c>
@@ -1486,10 +1484,10 @@
         <f t="shared" si="8"/>
         <v>157.27391874180864</v>
       </c>
-      <c r="H25" s="43" t="s">
+      <c r="H25" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="I25" s="44"/>
+      <c r="I25" s="58"/>
       <c r="J25" s="30">
         <v>1</v>
       </c>
@@ -1501,10 +1499,10 @@
       <c r="S25" s="1"/>
     </row>
     <row r="26" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="43" t="s">
+      <c r="B26" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="44"/>
+      <c r="C26" s="58"/>
       <c r="D26" s="9">
         <v>7</v>
       </c>
@@ -1516,10 +1514,10 @@
         <f t="shared" si="8"/>
         <v>220.18348623853211</v>
       </c>
-      <c r="H26" s="43" t="s">
+      <c r="H26" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="I26" s="44"/>
+      <c r="I26" s="58"/>
       <c r="J26" s="30">
         <v>1</v>
       </c>
@@ -1531,10 +1529,10 @@
       <c r="S26" s="1"/>
     </row>
     <row r="27" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="44"/>
+      <c r="C27" s="58"/>
       <c r="D27" s="9">
         <v>6</v>
       </c>
@@ -1546,10 +1544,10 @@
         <f t="shared" si="8"/>
         <v>188.72870249017038</v>
       </c>
-      <c r="H27" s="43" t="s">
+      <c r="H27" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="I27" s="44"/>
+      <c r="I27" s="58"/>
       <c r="J27" s="30">
         <v>1</v>
       </c>
@@ -1561,10 +1559,10 @@
       <c r="S27" s="1"/>
     </row>
     <row r="28" spans="2:19" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="43" t="s">
+      <c r="B28" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="44"/>
+      <c r="C28" s="58"/>
       <c r="D28" s="9">
         <v>2</v>
       </c>
@@ -1576,10 +1574,10 @@
         <f t="shared" si="8"/>
         <v>62.909567496723461</v>
       </c>
-      <c r="H28" s="43" t="s">
+      <c r="H28" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="I28" s="44"/>
+      <c r="I28" s="58"/>
       <c r="J28" s="30">
         <v>1</v>
       </c>
@@ -1591,10 +1589,10 @@
       <c r="S28" s="1"/>
     </row>
     <row r="29" spans="2:19" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="43" t="s">
+      <c r="B29" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="44"/>
+      <c r="C29" s="58"/>
       <c r="D29" s="9">
         <v>2</v>
       </c>
@@ -1606,10 +1604,10 @@
         <f t="shared" si="8"/>
         <v>62.909567496723461</v>
       </c>
-      <c r="H29" s="43" t="s">
+      <c r="H29" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="I29" s="44"/>
+      <c r="I29" s="58"/>
       <c r="J29" s="30">
         <v>2</v>
       </c>
@@ -1623,10 +1621,10 @@
       <c r="Q29"/>
     </row>
     <row r="30" spans="2:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="44"/>
+      <c r="C30" s="58"/>
       <c r="D30" s="9">
         <v>1</v>
       </c>
@@ -1638,10 +1636,10 @@
         <f t="shared" si="8"/>
         <v>31.454783748361731</v>
       </c>
-      <c r="H30" s="43" t="s">
+      <c r="H30" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="I30" s="44"/>
+      <c r="I30" s="58"/>
       <c r="J30" s="30">
         <v>1</v>
       </c>
@@ -1656,10 +1654,10 @@
       <c r="Q30"/>
     </row>
     <row r="31" spans="2:19" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="44"/>
+      <c r="C31" s="58"/>
       <c r="D31" s="9">
         <v>1</v>
       </c>
@@ -1671,10 +1669,10 @@
         <f t="shared" si="8"/>
         <v>31.454783748361731</v>
       </c>
-      <c r="H31" s="43" t="s">
+      <c r="H31" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="I31" s="44"/>
+      <c r="I31" s="58"/>
       <c r="J31" s="30">
         <v>2</v>
       </c>
@@ -1689,10 +1687,10 @@
       <c r="Q31"/>
     </row>
     <row r="32" spans="2:19" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="43" t="s">
+      <c r="B32" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="44"/>
+      <c r="C32" s="58"/>
       <c r="D32" s="9">
         <v>1</v>
       </c>
@@ -1704,10 +1702,10 @@
         <f t="shared" si="8"/>
         <v>31.454783748361731</v>
       </c>
-      <c r="H32" s="45" t="s">
+      <c r="H32" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="I32" s="46"/>
+      <c r="I32" s="69"/>
       <c r="J32" s="31">
         <f>SUM(J22:J31)</f>
         <v>13</v>
@@ -1723,10 +1721,10 @@
       <c r="Q32"/>
     </row>
     <row r="33" spans="2:17" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="43" t="s">
+      <c r="B33" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="44"/>
+      <c r="C33" s="58"/>
       <c r="D33" s="9">
         <v>1</v>
       </c>
@@ -1738,10 +1736,10 @@
         <f>E33/7.63</f>
         <v>31.454783748361731</v>
       </c>
-      <c r="H33" s="68"/>
-      <c r="I33" s="68"/>
-      <c r="J33" s="69"/>
-      <c r="K33" s="70"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="41"/>
       <c r="M33"/>
       <c r="N33"/>
       <c r="O33"/>
@@ -1749,10 +1747,10 @@
       <c r="Q33"/>
     </row>
     <row r="34" spans="2:17" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="43" t="s">
+      <c r="B34" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="44"/>
+      <c r="C34" s="58"/>
       <c r="D34" s="9">
         <v>1</v>
       </c>
@@ -1764,21 +1762,21 @@
         <f>E34/7.63</f>
         <v>31.454783748361731</v>
       </c>
-      <c r="H34" s="68"/>
-      <c r="I34" s="68"/>
-      <c r="J34" s="69"/>
-      <c r="K34" s="70"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="41"/>
       <c r="M34"/>
       <c r="N34"/>
       <c r="O34"/>
       <c r="P34"/>
       <c r="Q34"/>
     </row>
-    <row r="35" spans="2:17" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="43" t="s">
+    <row r="35" spans="2:17" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="44"/>
+      <c r="C35" s="58"/>
       <c r="D35" s="9">
         <v>3</v>
       </c>
@@ -1799,11 +1797,11 @@
       <c r="P35"/>
       <c r="Q35"/>
     </row>
-    <row r="36" spans="2:17" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="43" t="s">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B36" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="44"/>
+      <c r="C36" s="58"/>
       <c r="D36" s="9">
         <v>1</v>
       </c>
@@ -1825,10 +1823,10 @@
       <c r="Q36"/>
     </row>
     <row r="37" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="43" t="s">
+      <c r="B37" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="C37" s="44"/>
+      <c r="C37" s="58"/>
       <c r="D37" s="9">
         <v>6</v>
       </c>
@@ -1847,10 +1845,10 @@
       <c r="Q37"/>
     </row>
     <row r="38" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="43" t="s">
+      <c r="B38" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="44"/>
+      <c r="C38" s="58"/>
       <c r="D38" s="9">
         <v>5</v>
       </c>
@@ -1871,10 +1869,10 @@
       <c r="Q38"/>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B39" s="43" t="s">
+      <c r="B39" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="44"/>
+      <c r="C39" s="58"/>
       <c r="D39" s="9">
         <v>5</v>
       </c>
@@ -1895,10 +1893,10 @@
       <c r="Q39"/>
     </row>
     <row r="40" spans="2:17" ht="15" x14ac:dyDescent="0.3">
-      <c r="B40" s="43" t="s">
+      <c r="B40" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="44"/>
+      <c r="C40" s="58"/>
       <c r="D40" s="9">
         <v>2</v>
       </c>
@@ -1923,10 +1921,10 @@
       <c r="Q40"/>
     </row>
     <row r="41" spans="2:17" ht="15" x14ac:dyDescent="0.3">
-      <c r="B41" s="53" t="s">
+      <c r="B41" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="54"/>
+      <c r="C41" s="60"/>
       <c r="D41" s="22">
         <v>4</v>
       </c>
@@ -1951,10 +1949,10 @@
       <c r="Q41"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B42" s="45" t="s">
+      <c r="B42" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="69"/>
       <c r="D42" s="23">
         <f>SUM(D22:D41)</f>
         <v>67</v>
@@ -2445,34 +2443,10 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H32:I32"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="H20:K20"/>
     <mergeCell ref="B42:C42"/>
@@ -2489,10 +2463,34 @@
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Ejemplo_Calculo_Costos.xlsx
+++ b/Ejemplo_Calculo_Costos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aad5c92cd729ce53/Desktop/Canelon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="686" documentId="8_{73BCACF4-02CA-48FB-B2BD-168834A595B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D710F3A-CE42-478E-B6BC-24E254D0972B}"/>
+  <xr:revisionPtr revIDLastSave="695" documentId="8_{73BCACF4-02CA-48FB-B2BD-168834A595B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{164B0BD2-550D-4DAE-AB93-BCD3AF13A3AE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3A4320B7-4EBE-4B4B-8C38-391152CD5001}"/>
   </bookViews>
@@ -550,7 +550,64 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -559,6 +616,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -570,66 +630,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1033,15 +1033,15 @@
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="2:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
       <c r="I6" s="5"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -1050,10 +1050,10 @@
       <c r="N6" s="3"/>
     </row>
     <row r="7" spans="2:17" s="4" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="50"/>
+      <c r="C7" s="70"/>
       <c r="D7" s="35" t="s">
         <v>1</v>
       </c>
@@ -1077,10 +1077,10 @@
       <c r="N7" s="3"/>
     </row>
     <row r="8" spans="2:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="46"/>
+      <c r="C8" s="65"/>
       <c r="D8" s="36" t="s">
         <v>4</v>
       </c>
@@ -1107,10 +1107,10 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="2:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="46"/>
+      <c r="C9" s="65"/>
       <c r="D9" s="36" t="s">
         <v>4</v>
       </c>
@@ -1137,10 +1137,10 @@
       <c r="N9" s="3"/>
     </row>
     <row r="10" spans="2:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="46"/>
+      <c r="C10" s="65"/>
       <c r="D10" s="36" t="s">
         <v>6</v>
       </c>
@@ -1167,10 +1167,10 @@
       <c r="N10" s="3"/>
     </row>
     <row r="11" spans="2:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="46"/>
+      <c r="C11" s="65"/>
       <c r="D11" s="20" t="s">
         <v>4</v>
       </c>
@@ -1197,10 +1197,10 @@
       <c r="N11" s="3"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="48"/>
+      <c r="C12" s="68"/>
       <c r="D12" s="40" t="s">
         <v>13</v>
       </c>
@@ -1225,10 +1225,10 @@
       <c r="Q12"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="52"/>
+      <c r="C13" s="62"/>
       <c r="D13" s="37" t="s">
         <v>13</v>
       </c>
@@ -1239,11 +1239,11 @@
       </c>
       <c r="G13" s="38">
         <f>F42</f>
-        <v>2107.4705111402359</v>
+        <v>2138.9252948885978</v>
       </c>
       <c r="H13" s="39">
         <f>E42</f>
-        <v>16080</v>
+        <v>16320</v>
       </c>
       <c r="M13"/>
       <c r="N13"/>
@@ -1252,8 +1252,8 @@
       <c r="Q13"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="45"/>
-      <c r="C14" s="46"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="65"/>
       <c r="D14" s="10"/>
       <c r="E14" s="12"/>
       <c r="F14" s="14">
@@ -1270,8 +1270,8 @@
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="45"/>
-      <c r="C15" s="46"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="65"/>
       <c r="D15" s="10"/>
       <c r="E15" s="12"/>
       <c r="F15" s="14">
@@ -1288,8 +1288,8 @@
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="45"/>
-      <c r="C16" s="46"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="10"/>
       <c r="E16" s="12"/>
       <c r="F16" s="14">
@@ -1306,10 +1306,10 @@
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B17" s="53" t="s">
+      <c r="B17" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="54"/>
+      <c r="C17" s="63"/>
       <c r="D17" s="25"/>
       <c r="E17" s="11">
         <f>SUM(E8:E11)</f>
@@ -1321,11 +1321,11 @@
       </c>
       <c r="G17" s="15">
         <f>SUM(G8:G16)</f>
-        <v>4018.5845347313234</v>
+        <v>4050.0393184796858</v>
       </c>
       <c r="H17" s="16">
         <f>SUM(H8:H16)</f>
-        <v>30661.8</v>
+        <v>30901.8</v>
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.3">
@@ -1338,26 +1338,26 @@
       <c r="H18" s="18"/>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B20" s="65" t="s">
+      <c r="B20" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="65"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="65"/>
-      <c r="H20" s="66" t="s">
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="H20" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="67"/>
-      <c r="J20" s="67"/>
-      <c r="K20" s="68"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="51"/>
       <c r="R20" s="1"/>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B21" s="55" t="s">
+      <c r="B21" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="56"/>
+      <c r="C21" s="60"/>
       <c r="D21" s="19" t="s">
         <v>26</v>
       </c>
@@ -1367,10 +1367,10 @@
       <c r="F21" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="55" t="s">
+      <c r="H21" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="70"/>
+      <c r="I21" s="53"/>
       <c r="J21" s="29" t="s">
         <v>28</v>
       </c>
@@ -1381,10 +1381,10 @@
       <c r="S21" s="1"/>
     </row>
     <row r="22" spans="2:19" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="61" t="s">
+      <c r="B22" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="62"/>
+      <c r="C22" s="57"/>
       <c r="D22" s="9">
         <v>7</v>
       </c>
@@ -1396,10 +1396,10 @@
         <f>E22/7.63</f>
         <v>220.18348623853211</v>
       </c>
-      <c r="H22" s="57" t="s">
+      <c r="H22" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="I22" s="58"/>
+      <c r="I22" s="45"/>
       <c r="J22" s="30">
         <v>1</v>
       </c>
@@ -1411,10 +1411,10 @@
       <c r="S22" s="1"/>
     </row>
     <row r="23" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="62"/>
+      <c r="C23" s="57"/>
       <c r="D23" s="9">
         <v>2</v>
       </c>
@@ -1426,10 +1426,10 @@
         <f t="shared" ref="F23:F41" si="8">E23/7.63</f>
         <v>62.909567496723461</v>
       </c>
-      <c r="H23" s="57" t="s">
+      <c r="H23" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="I23" s="58"/>
+      <c r="I23" s="45"/>
       <c r="J23" s="30">
         <v>1</v>
       </c>
@@ -1440,10 +1440,10 @@
       <c r="Q23"/>
     </row>
     <row r="24" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="61" t="s">
+      <c r="B24" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="62"/>
+      <c r="C24" s="57"/>
       <c r="D24" s="9">
         <v>5</v>
       </c>
@@ -1455,10 +1455,10 @@
         <f t="shared" si="8"/>
         <v>157.27391874180864</v>
       </c>
-      <c r="H24" s="57" t="s">
+      <c r="H24" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="I24" s="58"/>
+      <c r="I24" s="45"/>
       <c r="J24" s="30">
         <v>2</v>
       </c>
@@ -1469,10 +1469,10 @@
       <c r="Q24"/>
     </row>
     <row r="25" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="63" t="s">
+      <c r="B25" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="64"/>
+      <c r="C25" s="59"/>
       <c r="D25" s="9">
         <v>5</v>
       </c>
@@ -1484,10 +1484,10 @@
         <f t="shared" si="8"/>
         <v>157.27391874180864</v>
       </c>
-      <c r="H25" s="57" t="s">
+      <c r="H25" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="I25" s="58"/>
+      <c r="I25" s="45"/>
       <c r="J25" s="30">
         <v>1</v>
       </c>
@@ -1499,10 +1499,10 @@
       <c r="S25" s="1"/>
     </row>
     <row r="26" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="58"/>
+      <c r="C26" s="45"/>
       <c r="D26" s="9">
         <v>7</v>
       </c>
@@ -1514,10 +1514,10 @@
         <f t="shared" si="8"/>
         <v>220.18348623853211</v>
       </c>
-      <c r="H26" s="57" t="s">
+      <c r="H26" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="I26" s="58"/>
+      <c r="I26" s="45"/>
       <c r="J26" s="30">
         <v>1</v>
       </c>
@@ -1529,10 +1529,10 @@
       <c r="S26" s="1"/>
     </row>
     <row r="27" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="58"/>
+      <c r="C27" s="45"/>
       <c r="D27" s="9">
         <v>6</v>
       </c>
@@ -1544,10 +1544,10 @@
         <f t="shared" si="8"/>
         <v>188.72870249017038</v>
       </c>
-      <c r="H27" s="57" t="s">
+      <c r="H27" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="I27" s="58"/>
+      <c r="I27" s="45"/>
       <c r="J27" s="30">
         <v>1</v>
       </c>
@@ -1558,11 +1558,11 @@
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
     </row>
-    <row r="28" spans="2:19" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="57" t="s">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B28" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="58"/>
+      <c r="C28" s="45"/>
       <c r="D28" s="9">
         <v>2</v>
       </c>
@@ -1574,10 +1574,10 @@
         <f t="shared" si="8"/>
         <v>62.909567496723461</v>
       </c>
-      <c r="H28" s="57" t="s">
+      <c r="H28" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="I28" s="58"/>
+      <c r="I28" s="45"/>
       <c r="J28" s="30">
         <v>1</v>
       </c>
@@ -1588,26 +1588,26 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="2:19" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="57" t="s">
+    <row r="29" spans="2:19" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="58"/>
+      <c r="C29" s="45"/>
       <c r="D29" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="21">
         <f t="shared" si="9"/>
-        <v>480</v>
+        <v>720</v>
       </c>
       <c r="F29" s="32">
         <f t="shared" si="8"/>
-        <v>62.909567496723461</v>
-      </c>
-      <c r="H29" s="57" t="s">
+        <v>94.364351245085189</v>
+      </c>
+      <c r="H29" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="I29" s="58"/>
+      <c r="I29" s="45"/>
       <c r="J29" s="30">
         <v>2</v>
       </c>
@@ -1620,11 +1620,11 @@
       <c r="P29"/>
       <c r="Q29"/>
     </row>
-    <row r="30" spans="2:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="57" t="s">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B30" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="58"/>
+      <c r="C30" s="45"/>
       <c r="D30" s="9">
         <v>1</v>
       </c>
@@ -1636,10 +1636,10 @@
         <f t="shared" si="8"/>
         <v>31.454783748361731</v>
       </c>
-      <c r="H30" s="57" t="s">
+      <c r="H30" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="I30" s="58"/>
+      <c r="I30" s="45"/>
       <c r="J30" s="30">
         <v>1</v>
       </c>
@@ -1653,11 +1653,11 @@
       <c r="P30"/>
       <c r="Q30"/>
     </row>
-    <row r="31" spans="2:19" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="57" t="s">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B31" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="58"/>
+      <c r="C31" s="45"/>
       <c r="D31" s="9">
         <v>1</v>
       </c>
@@ -1669,10 +1669,10 @@
         <f t="shared" si="8"/>
         <v>31.454783748361731</v>
       </c>
-      <c r="H31" s="57" t="s">
+      <c r="H31" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="I31" s="58"/>
+      <c r="I31" s="45"/>
       <c r="J31" s="30">
         <v>2</v>
       </c>
@@ -1686,11 +1686,11 @@
       <c r="P31"/>
       <c r="Q31"/>
     </row>
-    <row r="32" spans="2:19" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="57" t="s">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B32" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="58"/>
+      <c r="C32" s="45"/>
       <c r="D32" s="9">
         <v>1</v>
       </c>
@@ -1702,10 +1702,10 @@
         <f t="shared" si="8"/>
         <v>31.454783748361731</v>
       </c>
-      <c r="H32" s="53" t="s">
+      <c r="H32" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="I32" s="69"/>
+      <c r="I32" s="47"/>
       <c r="J32" s="31">
         <f>SUM(J22:J31)</f>
         <v>13</v>
@@ -1720,11 +1720,11 @@
       <c r="P32"/>
       <c r="Q32"/>
     </row>
-    <row r="33" spans="2:17" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="57" t="s">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B33" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="58"/>
+      <c r="C33" s="45"/>
       <c r="D33" s="9">
         <v>1</v>
       </c>
@@ -1746,11 +1746,11 @@
       <c r="P33"/>
       <c r="Q33"/>
     </row>
-    <row r="34" spans="2:17" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="57" t="s">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B34" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="58"/>
+      <c r="C34" s="45"/>
       <c r="D34" s="9">
         <v>1</v>
       </c>
@@ -1773,10 +1773,10 @@
       <c r="Q34"/>
     </row>
     <row r="35" spans="2:17" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="57" t="s">
+      <c r="B35" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="58"/>
+      <c r="C35" s="45"/>
       <c r="D35" s="9">
         <v>3</v>
       </c>
@@ -1798,10 +1798,10 @@
       <c r="Q35"/>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B36" s="57" t="s">
+      <c r="B36" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="58"/>
+      <c r="C36" s="45"/>
       <c r="D36" s="9">
         <v>1</v>
       </c>
@@ -1823,10 +1823,10 @@
       <c r="Q36"/>
     </row>
     <row r="37" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="57" t="s">
+      <c r="B37" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="C37" s="58"/>
+      <c r="C37" s="45"/>
       <c r="D37" s="9">
         <v>6</v>
       </c>
@@ -1845,10 +1845,10 @@
       <c r="Q37"/>
     </row>
     <row r="38" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="57" t="s">
+      <c r="B38" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="58"/>
+      <c r="C38" s="45"/>
       <c r="D38" s="9">
         <v>5</v>
       </c>
@@ -1869,10 +1869,10 @@
       <c r="Q38"/>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B39" s="57" t="s">
+      <c r="B39" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="58"/>
+      <c r="C39" s="45"/>
       <c r="D39" s="9">
         <v>5</v>
       </c>
@@ -1893,10 +1893,10 @@
       <c r="Q39"/>
     </row>
     <row r="40" spans="2:17" ht="15" x14ac:dyDescent="0.3">
-      <c r="B40" s="57" t="s">
+      <c r="B40" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="58"/>
+      <c r="C40" s="45"/>
       <c r="D40" s="9">
         <v>2</v>
       </c>
@@ -1921,10 +1921,10 @@
       <c r="Q40"/>
     </row>
     <row r="41" spans="2:17" ht="15" x14ac:dyDescent="0.3">
-      <c r="B41" s="59" t="s">
+      <c r="B41" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="60"/>
+      <c r="C41" s="55"/>
       <c r="D41" s="22">
         <v>4</v>
       </c>
@@ -1949,21 +1949,21 @@
       <c r="Q41"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B42" s="53" t="s">
+      <c r="B42" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="69"/>
+      <c r="C42" s="47"/>
       <c r="D42" s="23">
         <f>SUM(D22:D41)</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E42" s="28">
         <f t="shared" si="9"/>
-        <v>16080</v>
+        <v>16320</v>
       </c>
       <c r="F42" s="33">
         <f>E42/7.63</f>
-        <v>2107.4705111402359</v>
+        <v>2138.9252948885978</v>
       </c>
       <c r="G42"/>
       <c r="H42"/>
@@ -2443,47 +2443,6 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
@@ -2491,6 +2450,47 @@
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
